--- a/results/dashboard.xlsx
+++ b/results/dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gixium/Repos/CLLM-SenteTruth-replication-study/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731BCC9C-A9D5-DB4E-BA9B-79FF1801CA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC24FA4-6D85-3740-8CEA-EBC37264AB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="1480" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4460" yWindow="-20960" windowWidth="38320" windowHeight="20920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,6 @@
     <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/results/dashboard.xlsx
+++ b/results/dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gixium/Repos/CLLM-SenteTruth-replication-study/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC24FA4-6D85-3740-8CEA-EBC37264AB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB181D6C-96A0-9143-AB58-9AEE1E624B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4460" yWindow="-20960" windowWidth="38320" windowHeight="20920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,9 +41,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="22">
-  <si>
-    <t>Blockchain LLM Oracle — Comprehensive Temperature &amp; Seed Comparison</t>
-  </si>
   <si>
     <t>Condition</t>
   </si>
@@ -106,6 +103,9 @@
   </si>
   <si>
     <t>Round</t>
+  </si>
+  <si>
+    <t>final deltas</t>
   </si>
 </sst>
 </file>
@@ -354,7 +354,14 @@
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -473,7 +480,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EAEC-4D49-857D-2DCC8ABFACD6}"/>
+              <c16:uniqueId val="{00000000-50AE-1B48-B355-B74F3E5513A6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -561,7 +568,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EAEC-4D49-857D-2DCC8ABFACD6}"/>
+              <c16:uniqueId val="{00000001-50AE-1B48-B355-B74F3E5513A6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -603,7 +610,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-EAEC-4D49-857D-2DCC8ABFACD6}"/>
+                  <c16:uniqueId val="{00000002-50AE-1B48-B355-B74F3E5513A6}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -670,7 +677,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-EAEC-4D49-857D-2DCC8ABFACD6}"/>
+              <c16:uniqueId val="{00000003-50AE-1B48-B355-B74F3E5513A6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -758,7 +765,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-EAEC-4D49-857D-2DCC8ABFACD6}"/>
+              <c16:uniqueId val="{00000004-50AE-1B48-B355-B74F3E5513A6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5774,22 +5781,24 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>33867</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7920000" cy="4320000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{771FFA9D-B44A-7D49-BA2E-A4A41728BDF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5801,122 +5810,6 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>154217</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>181429</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1412566" cy="264560"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D5DA2A4-609D-BB09-F54E-06567A2E0FA7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9815288" y="2140858"/>
-          <a:ext cx="1412566" cy="264560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100"/>
-            <a:t>60/40 MIX 100 nodes</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1222831</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>134258</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1354666" cy="264560"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A607E5DC-95C0-3F4E-AA29-53B099ECEC74}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11555188" y="5903687"/>
-          <a:ext cx="1354666" cy="264560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100"/>
-            <a:t>60/40 PRO 60 nodes</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
@@ -6268,6 +6161,304 @@
       </cdr:txBody>
     </cdr:sp>
   </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.09782</cdr:x>
+      <cdr:y>0.03528</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.27617</cdr:x>
+      <cdr:y>0.09652</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="5" name="TextBox 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D5DA2A4-609D-BB09-F54E-06567A2E0FA7}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="774700" y="152400"/>
+          <a:ext cx="1412566" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>60/40 MIX 100 nodes</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.33514</cdr:x>
+      <cdr:y>0.88488</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.50618</cdr:x>
+      <cdr:y>0.94613</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="6" name="TextBox 3">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A607E5DC-95C0-3F4E-AA29-53B099ECEC74}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="2654300" y="3822700"/>
+          <a:ext cx="1354666" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>60/40 PRO 60 nodes</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
 </c:userShapes>
 </file>
 
@@ -13719,54 +13910,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="1"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="8">
         <f>[1]gpt4omini_single_100!O5</f>
@@ -13793,7 +13985,7 @@
         <v>0.99</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M5" s="5">
         <f>E5</f>
@@ -13814,10 +14006,10 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="13">
         <f>[2]gpt4omini_single_100!O5</f>
@@ -13844,7 +14036,7 @@
         <v>0.01</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M6">
         <f>E9</f>
@@ -13865,10 +14057,10 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="18">
         <f>[3]gpt4omini_single_100!O5</f>
@@ -13895,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M7">
         <f>E13</f>
@@ -13916,10 +14108,10 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="23">
         <f>[4]gpt4omini_single_100!O5</f>
@@ -13946,7 +14138,7 @@
         <v>0.97</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M8">
         <f>E17</f>
@@ -13967,10 +14159,10 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="8">
         <f>[1]gpt4omini_single_60!O5</f>
@@ -13999,10 +14191,10 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="13">
         <f>[2]gpt4omini_single_60!O5</f>
@@ -14031,10 +14223,10 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="18">
         <f>[3]gpt4omini_single_60!O5</f>
@@ -14063,10 +14255,10 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="23">
         <f>[4]gpt4omini_single_60!O5</f>
@@ -14095,10 +14287,10 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="8">
         <f>[1]gpt4omini_single_100_2!O5</f>
@@ -14127,10 +14319,10 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="13">
         <f>[2]gpt4omini_single_100_2!O5</f>
@@ -14159,10 +14351,10 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="18">
         <f>[3]gpt4omini_single_100_2!O5</f>
@@ -14191,10 +14383,10 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="23">
         <f>[4]gpt4omini_single_100_2!O5</f>
@@ -14223,10 +14415,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="8">
         <f>[1]gpt4omini_single_60_2!O5</f>
@@ -14255,10 +14447,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="13">
         <f>[2]gpt4omini_single_60_2!O5</f>
@@ -14287,10 +14479,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="18">
         <f>[3]gpt4omini_single_60_2!O5</f>
@@ -14319,10 +14511,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" s="28">
         <f>[4]gpt4omini_single_60_2!O5</f>
@@ -14363,78 +14555,78 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" t="s">
         <v>9</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>10</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" t="s">
-        <v>12</v>
-      </c>
       <c r="S2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" t="s">
         <v>9</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>10</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>11</v>
-      </c>
-      <c r="W2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">

--- a/results/dashboard.xlsx
+++ b/results/dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gixium/Repos/CLLM-SenteTruth-replication-study/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB181D6C-96A0-9143-AB58-9AEE1E624B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAAC6AC-47EA-CD47-9442-B3AF0DFBA27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4460" yWindow="-20960" windowWidth="38320" windowHeight="20920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="500" yWindow="-21000" windowWidth="26980" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -5857,12 +5857,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.55734</cdr:x>
-      <cdr:y>0.12305</cdr:y>
+      <cdr:x>0.54708</cdr:x>
+      <cdr:y>0.91092</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.7357</cdr:x>
-      <cdr:y>0.18429</cdr:y>
+      <cdr:x>0.72544</cdr:x>
+      <cdr:y>0.97216</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -5877,8 +5877,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4414157" y="531586"/>
-          <a:ext cx="1412566" cy="264560"/>
+          <a:off x="4332853" y="3935176"/>
+          <a:ext cx="1412611" cy="264557"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6006,12 +6006,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.80704</cdr:x>
-      <cdr:y>0.9042</cdr:y>
+      <cdr:x>0.79934</cdr:x>
+      <cdr:y>0.91596</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.97808</cdr:x>
-      <cdr:y>0.96544</cdr:y>
+      <cdr:x>0.97038</cdr:x>
+      <cdr:y>0.9772</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6026,8 +6026,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="6391729" y="3906157"/>
-          <a:ext cx="1354666" cy="264560"/>
+          <a:off x="6330797" y="3956944"/>
+          <a:ext cx="1354637" cy="264557"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6163,12 +6163,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.09782</cdr:x>
-      <cdr:y>0.03528</cdr:y>
+      <cdr:x>0.07729</cdr:x>
+      <cdr:y>0.90782</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.27617</cdr:x>
-      <cdr:y>0.09652</cdr:y>
+      <cdr:x>0.25564</cdr:x>
+      <cdr:y>0.96906</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6183,8 +6183,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="774700" y="152400"/>
-          <a:ext cx="1412566" cy="264560"/>
+          <a:off x="612174" y="3921770"/>
+          <a:ext cx="1412532" cy="264556"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6312,12 +6312,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.33514</cdr:x>
-      <cdr:y>0.88488</cdr:y>
+      <cdr:x>0.3159</cdr:x>
+      <cdr:y>0.91075</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.50618</cdr:x>
-      <cdr:y>0.94613</cdr:y>
+      <cdr:x>0.48694</cdr:x>
+      <cdr:y>0.972</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6332,8 +6332,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2654300" y="3822700"/>
-          <a:ext cx="1354666" cy="264560"/>
+          <a:off x="2501909" y="3934442"/>
+          <a:ext cx="1354637" cy="264600"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>

--- a/results/dashboard.xlsx
+++ b/results/dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CC08A9-DB78-4F44-9B41-B6E43032DDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="charts" sheetId="6" r:id="rId1"/>
